--- a/data/employees/EMP066/AST-EMP066-06.xlsx
+++ b/data/employees/EMP066/AST-EMP066-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,215 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Skills Matrix - Avery Wilson (HR)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Avery Wilson | Role: Manager | Location: Fremont | Date: 2025-03-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp066 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp066 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>98</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Employee ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Skills</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Last Review Date</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Rating</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp066 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>68</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EMP006</t>
+          <t>EMP066</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Avery Wilson</t>
+          <t>Ast Emp066 06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>2026-W04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Specialist</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Azure AI, Fabric</t>
-        </is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>85</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>4.2</v>
+          <t>Section 1: Operational risk review. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EMP011</t>
+          <t>EMP066</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alex Garcia</t>
+          <t>Ast Emp066 06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>2026-W05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Lead</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Synapse, TypeScript</t>
-        </is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>81</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>3.9</v>
+          <t>Section 1: Operational risk review. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EMP016</t>
+          <t>EMP066</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Avery Wilson</t>
+          <t>Ast Emp066 06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Python, SQL</t>
-        </is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>78</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>4.5</v>
+          <t>Section 1: Quarterly delivery milestones. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EMP021</t>
+          <t>EMP066</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alex Garcia</t>
+          <t>Ast Emp066 06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>76</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp066 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>96</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp066 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>92</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp066 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>71</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp066 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>88</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp066 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>77</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp066 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>94</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp066 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>96</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp066 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>82</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp066 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>78</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp066 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>67</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp066 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>79</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp066 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>73</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp066 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>78</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp066 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>64</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp066 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>87</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp066 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>94</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp066 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>96</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ontology, MLOps</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>4</v>
+          <t>Section 1: Quarterly delivery milestones. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP066</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP066 contributes to ast emp066 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>